--- a/config/union/history.xlsx
+++ b/config/union/history.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="history" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="history" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>#C0x5C9970#%s#C0x5B545B#がギルドに加入しました！</t>
+          <t>#C0x5C9970#%s#C0x5B545B#加入公会了！</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>#C0x5C9970#%s#C0x5B545B#がギルドを脱退しました！</t>
+          <t>#C0x5C9970#%s#C0x5B545B#退出了公会！</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>#C0x5C9970#%s#C0x5B545B#は#C0x5C9970#%s#C0x5B545B#にギルドから追放されました！</t>
+          <t>#C0x5C9970#%s#C0x5B545B#在#C0x5C9970#%s#C0x5B545B#被公会开除了！</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>#C0x5C9970#%s#C0x5B545B#が副会長に昇格しました！</t>
+          <t>#C0x5C9970#%s#C0x5B545B#晋升为副会长了！</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>#C0x5C9970#%s#C0x5B545B#が一般に降格しました！</t>
+          <t>#C0x5C9970#%s#C0x5B545B#一般降级了！</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>#C0x5C9970#%s#C0x5B545B#が会長の座を{0}に譲渡しました！</t>
+          <t>#C0x5C9970#%s#C0x5B545B#把会长的位置让给{0}了！</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>#C0x5C9970#%s#C0x5B545B#が新会長に就任しました！</t>
+          <t>#C0x5C9970#%s#C0x5B545B#就任新会长了！</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>#C0x5C9970#%s#C0x5B545B#が#C0x5C9970#%s#C0x5B545B#の加入承認をしました！</t>
+          <t>#C0x5C9970#%s#C0x5B545B#已批准#C0x5C9970#%s#C0x5B545B#的加入！</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
